--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2756-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2756-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34229A42-D109-49A1-AA4D-499039D77220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D47B5DC-011F-4252-A58D-3952923C528F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E40CF902-88C5-4CAF-A701-333ED036F8C3}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C595BF1F-FFF6-4E8E-A390-CC20AE3F9B07}"/>
   </bookViews>
   <sheets>
     <sheet name="2756-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1561,25 +1561,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E665F4-0DAC-41F2-B22B-4167550CDC05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5BB3CA8-368F-40C3-B004-FD9A664FBC46}">
   <dimension ref="A1:X44"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="23" width="6.75" customWidth="1"/>
-    <col min="24" max="24" width="9.125" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="23" width="5.88671875" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1613,7 +1613,7 @@
       <c r="W1" s="34"/>
       <c r="X1" s="26"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1649,7 +1649,7 @@
       <c r="W2" s="36"/>
       <c r="X2" s="37"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="X3" s="40"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1769,7 +1769,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="41">
         <v>2025</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1877,7 +1877,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>30</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>30</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="51">
         <v>2024</v>
       </c>
@@ -2171,7 +2171,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>30</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>30</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>30</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>30</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="53">
         <v>2023</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>6.08</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>30</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>30</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>30</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>30</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>30</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="51">
         <v>2022</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="55" t="s">
         <v>30</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="56"/>
       <c r="B24" s="56"/>
       <c r="C24" s="22" t="s">
@@ -3157,7 +3157,7 @@
       <c r="W24" s="62"/>
       <c r="X24" s="58"/>
     </row>
-    <row r="25" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>30</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
         <v>30</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
         <v>30</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>30</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="53">
         <v>2021</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="45" t="s">
         <v>30</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="46"/>
       <c r="B31" s="46"/>
       <c r="C31" s="24" t="s">
@@ -3627,7 +3627,7 @@
       <c r="W31" s="50"/>
       <c r="X31" s="48"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>30</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>30</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>30</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="51">
         <v>2020</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
         <v>30</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="18" t="s">
         <v>30</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
         <v>30</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="18" t="s">
         <v>30</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <v>2019</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>30</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>30</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>30</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="51" t="s">
         <v>46</v>
       </c>
